--- a/output/テレッサ_実地調査用モック_dhpケアマネジメント_2026年10月.xlsx
+++ b/output/テレッサ_実地調査用モック_dhpケアマネジメント_2026年10月.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>大阪市（2級地） 訪問介護 11.40円/単位（2027年4月改定で見直し）</t>
+          <t>大阪市（2級地） 訪問介護 11.12円/単位（2027年4月改定で見直し）</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
         <v>387</v>
       </c>
       <c r="L2" s="10">
-        <f>ROUNDDOWN(K2*11.4,0)</f>
+        <f>ROUNDDOWN(K2*11.12,0)</f>
         <v/>
       </c>
       <c r="M2" s="11" t="inlineStr">
@@ -1276,7 +1276,7 @@
         <v>179</v>
       </c>
       <c r="L3" s="10">
-        <f>ROUNDDOWN(K3*11.4,0)</f>
+        <f>ROUNDDOWN(K3*11.12,0)</f>
         <v/>
       </c>
       <c r="M3" s="11" t="inlineStr">
@@ -1347,7 +1347,7 @@
         <v>309</v>
       </c>
       <c r="L4" s="10">
-        <f>ROUNDDOWN(K4*11.4,0)</f>
+        <f>ROUNDDOWN(K4*11.12,0)</f>
         <v/>
       </c>
       <c r="M4" s="11" t="inlineStr">
@@ -1418,7 +1418,7 @@
         <v>220</v>
       </c>
       <c r="L5" s="10">
-        <f>ROUNDDOWN(K5*11.4,0)</f>
+        <f>ROUNDDOWN(K5*11.12,0)</f>
         <v/>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -1489,7 +1489,7 @@
         <v>244</v>
       </c>
       <c r="L6" s="10">
-        <f>ROUNDDOWN(K6*11.4,0)</f>
+        <f>ROUNDDOWN(K6*11.12,0)</f>
         <v/>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1560,7 +1560,7 @@
         <v>244</v>
       </c>
       <c r="L7" s="10">
-        <f>ROUNDDOWN(K7*11.4,0)</f>
+        <f>ROUNDDOWN(K7*11.12,0)</f>
         <v/>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1631,7 +1631,7 @@
         <v>387</v>
       </c>
       <c r="L8" s="10">
-        <f>ROUNDDOWN(K8*11.4,0)</f>
+        <f>ROUNDDOWN(K8*11.12,0)</f>
         <v/>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1702,7 +1702,7 @@
         <v>309</v>
       </c>
       <c r="L9" s="10">
-        <f>ROUNDDOWN(K9*11.4,0)</f>
+        <f>ROUNDDOWN(K9*11.12,0)</f>
         <v/>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1773,7 +1773,7 @@
         <v>387</v>
       </c>
       <c r="L10" s="10">
-        <f>ROUNDDOWN(K10*11.4,0)</f>
+        <f>ROUNDDOWN(K10*11.12,0)</f>
         <v/>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1844,7 +1844,7 @@
         <v>244</v>
       </c>
       <c r="L11" s="10">
-        <f>ROUNDDOWN(K11*11.4,0)</f>
+        <f>ROUNDDOWN(K11*11.12,0)</f>
         <v/>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1915,7 +1915,7 @@
         <v>244</v>
       </c>
       <c r="L12" s="10">
-        <f>ROUNDDOWN(K12*11.4,0)</f>
+        <f>ROUNDDOWN(K12*11.12,0)</f>
         <v/>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1986,7 +1986,7 @@
         <v>387</v>
       </c>
       <c r="L13" s="10">
-        <f>ROUNDDOWN(K13*11.4,0)</f>
+        <f>ROUNDDOWN(K13*11.12,0)</f>
         <v/>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -2057,7 +2057,7 @@
         <v>220</v>
       </c>
       <c r="L14" s="10">
-        <f>ROUNDDOWN(K14*11.4,0)</f>
+        <f>ROUNDDOWN(K14*11.12,0)</f>
         <v/>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -2128,7 +2128,7 @@
         <v>387</v>
       </c>
       <c r="L15" s="10">
-        <f>ROUNDDOWN(K15*11.4,0)</f>
+        <f>ROUNDDOWN(K15*11.12,0)</f>
         <v/>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -2199,7 +2199,7 @@
         <v>244</v>
       </c>
       <c r="L16" s="10">
-        <f>ROUNDDOWN(K16*11.4,0)</f>
+        <f>ROUNDDOWN(K16*11.12,0)</f>
         <v/>
       </c>
       <c r="M16" s="11" t="inlineStr">
@@ -2270,7 +2270,7 @@
         <v>244</v>
       </c>
       <c r="L17" s="10">
-        <f>ROUNDDOWN(K17*11.4,0)</f>
+        <f>ROUNDDOWN(K17*11.12,0)</f>
         <v/>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -2341,7 +2341,7 @@
         <v>387</v>
       </c>
       <c r="L18" s="10">
-        <f>ROUNDDOWN(K18*11.4,0)</f>
+        <f>ROUNDDOWN(K18*11.12,0)</f>
         <v/>
       </c>
       <c r="M18" s="11" t="inlineStr">
@@ -2412,7 +2412,7 @@
         <v>179</v>
       </c>
       <c r="L19" s="10">
-        <f>ROUNDDOWN(K19*11.4,0)</f>
+        <f>ROUNDDOWN(K19*11.12,0)</f>
         <v/>
       </c>
       <c r="M19" s="11" t="inlineStr">
@@ -2483,7 +2483,7 @@
         <v>309</v>
       </c>
       <c r="L20" s="10">
-        <f>ROUNDDOWN(K20*11.4,0)</f>
+        <f>ROUNDDOWN(K20*11.12,0)</f>
         <v/>
       </c>
       <c r="M20" s="11" t="inlineStr">
@@ -2554,7 +2554,7 @@
         <v>220</v>
       </c>
       <c r="L21" s="10">
-        <f>ROUNDDOWN(K21*11.4,0)</f>
+        <f>ROUNDDOWN(K21*11.12,0)</f>
         <v/>
       </c>
       <c r="M21" s="11" t="inlineStr">
@@ -2625,7 +2625,7 @@
         <v>244</v>
       </c>
       <c r="L22" s="10">
-        <f>ROUNDDOWN(K22*11.4,0)</f>
+        <f>ROUNDDOWN(K22*11.12,0)</f>
         <v/>
       </c>
       <c r="M22" s="11" t="inlineStr">
@@ -2696,7 +2696,7 @@
         <v>244</v>
       </c>
       <c r="L23" s="10">
-        <f>ROUNDDOWN(K23*11.4,0)</f>
+        <f>ROUNDDOWN(K23*11.12,0)</f>
         <v/>
       </c>
       <c r="M23" s="11" t="inlineStr">
@@ -2767,7 +2767,7 @@
         <v>387</v>
       </c>
       <c r="L24" s="10">
-        <f>ROUNDDOWN(K24*11.4,0)</f>
+        <f>ROUNDDOWN(K24*11.12,0)</f>
         <v/>
       </c>
       <c r="M24" s="11" t="inlineStr">
@@ -2838,7 +2838,7 @@
         <v>309</v>
       </c>
       <c r="L25" s="10">
-        <f>ROUNDDOWN(K25*11.4,0)</f>
+        <f>ROUNDDOWN(K25*11.12,0)</f>
         <v/>
       </c>
       <c r="M25" s="11" t="inlineStr">
@@ -2909,7 +2909,7 @@
         <v>387</v>
       </c>
       <c r="L26" s="10">
-        <f>ROUNDDOWN(K26*11.4,0)</f>
+        <f>ROUNDDOWN(K26*11.12,0)</f>
         <v/>
       </c>
       <c r="M26" s="11" t="inlineStr">
@@ -2980,7 +2980,7 @@
         <v>244</v>
       </c>
       <c r="L27" s="10">
-        <f>ROUNDDOWN(K27*11.4,0)</f>
+        <f>ROUNDDOWN(K27*11.12,0)</f>
         <v/>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -3051,7 +3051,7 @@
         <v>244</v>
       </c>
       <c r="L28" s="10">
-        <f>ROUNDDOWN(K28*11.4,0)</f>
+        <f>ROUNDDOWN(K28*11.12,0)</f>
         <v/>
       </c>
       <c r="M28" s="11" t="inlineStr">
@@ -3122,7 +3122,7 @@
         <v>387</v>
       </c>
       <c r="L29" s="10">
-        <f>ROUNDDOWN(K29*11.4,0)</f>
+        <f>ROUNDDOWN(K29*11.12,0)</f>
         <v/>
       </c>
       <c r="M29" s="11" t="inlineStr">
@@ -3193,7 +3193,7 @@
         <v>220</v>
       </c>
       <c r="L30" s="10">
-        <f>ROUNDDOWN(K30*11.4,0)</f>
+        <f>ROUNDDOWN(K30*11.12,0)</f>
         <v/>
       </c>
       <c r="M30" s="11" t="inlineStr">
@@ -3264,7 +3264,7 @@
         <v>387</v>
       </c>
       <c r="L31" s="10">
-        <f>ROUNDDOWN(K31*11.4,0)</f>
+        <f>ROUNDDOWN(K31*11.12,0)</f>
         <v/>
       </c>
       <c r="M31" s="11" t="inlineStr">
@@ -3335,7 +3335,7 @@
         <v>244</v>
       </c>
       <c r="L32" s="10">
-        <f>ROUNDDOWN(K32*11.4,0)</f>
+        <f>ROUNDDOWN(K32*11.12,0)</f>
         <v/>
       </c>
       <c r="M32" s="11" t="inlineStr">
@@ -3406,7 +3406,7 @@
         <v>244</v>
       </c>
       <c r="L33" s="10">
-        <f>ROUNDDOWN(K33*11.4,0)</f>
+        <f>ROUNDDOWN(K33*11.12,0)</f>
         <v/>
       </c>
       <c r="M33" s="11" t="inlineStr">
@@ -3477,7 +3477,7 @@
         <v>387</v>
       </c>
       <c r="L34" s="10">
-        <f>ROUNDDOWN(K34*11.4,0)</f>
+        <f>ROUNDDOWN(K34*11.12,0)</f>
         <v/>
       </c>
       <c r="M34" s="11" t="inlineStr">
@@ -3548,7 +3548,7 @@
         <v>179</v>
       </c>
       <c r="L35" s="10">
-        <f>ROUNDDOWN(K35*11.4,0)</f>
+        <f>ROUNDDOWN(K35*11.12,0)</f>
         <v/>
       </c>
       <c r="M35" s="11" t="inlineStr">
@@ -3619,7 +3619,7 @@
         <v>309</v>
       </c>
       <c r="L36" s="10">
-        <f>ROUNDDOWN(K36*11.4,0)</f>
+        <f>ROUNDDOWN(K36*11.12,0)</f>
         <v/>
       </c>
       <c r="M36" s="11" t="inlineStr">
@@ -3690,7 +3690,7 @@
         <v>220</v>
       </c>
       <c r="L37" s="10">
-        <f>ROUNDDOWN(K37*11.4,0)</f>
+        <f>ROUNDDOWN(K37*11.12,0)</f>
         <v/>
       </c>
       <c r="M37" s="11" t="inlineStr">
@@ -3761,7 +3761,7 @@
         <v>244</v>
       </c>
       <c r="L38" s="10">
-        <f>ROUNDDOWN(K38*11.4,0)</f>
+        <f>ROUNDDOWN(K38*11.12,0)</f>
         <v/>
       </c>
       <c r="M38" s="11" t="inlineStr">
@@ -3832,7 +3832,7 @@
         <v>244</v>
       </c>
       <c r="L39" s="10">
-        <f>ROUNDDOWN(K39*11.4,0)</f>
+        <f>ROUNDDOWN(K39*11.12,0)</f>
         <v/>
       </c>
       <c r="M39" s="11" t="inlineStr">
@@ -3903,7 +3903,7 @@
         <v>387</v>
       </c>
       <c r="L40" s="10">
-        <f>ROUNDDOWN(K40*11.4,0)</f>
+        <f>ROUNDDOWN(K40*11.12,0)</f>
         <v/>
       </c>
       <c r="M40" s="11" t="inlineStr">
@@ -3974,7 +3974,7 @@
         <v>309</v>
       </c>
       <c r="L41" s="10">
-        <f>ROUNDDOWN(K41*11.4,0)</f>
+        <f>ROUNDDOWN(K41*11.12,0)</f>
         <v/>
       </c>
       <c r="M41" s="11" t="inlineStr">
@@ -4045,7 +4045,7 @@
         <v>387</v>
       </c>
       <c r="L42" s="10">
-        <f>ROUNDDOWN(K42*11.4,0)</f>
+        <f>ROUNDDOWN(K42*11.12,0)</f>
         <v/>
       </c>
       <c r="M42" s="11" t="inlineStr">
@@ -4116,7 +4116,7 @@
         <v>244</v>
       </c>
       <c r="L43" s="10">
-        <f>ROUNDDOWN(K43*11.4,0)</f>
+        <f>ROUNDDOWN(K43*11.12,0)</f>
         <v/>
       </c>
       <c r="M43" s="11" t="inlineStr">
@@ -4187,7 +4187,7 @@
         <v>244</v>
       </c>
       <c r="L44" s="10">
-        <f>ROUNDDOWN(K44*11.4,0)</f>
+        <f>ROUNDDOWN(K44*11.12,0)</f>
         <v/>
       </c>
       <c r="M44" s="11" t="inlineStr">
@@ -4258,7 +4258,7 @@
         <v>387</v>
       </c>
       <c r="L45" s="10">
-        <f>ROUNDDOWN(K45*11.4,0)</f>
+        <f>ROUNDDOWN(K45*11.12,0)</f>
         <v/>
       </c>
       <c r="M45" s="11" t="inlineStr">
@@ -4329,7 +4329,7 @@
         <v>220</v>
       </c>
       <c r="L46" s="10">
-        <f>ROUNDDOWN(K46*11.4,0)</f>
+        <f>ROUNDDOWN(K46*11.12,0)</f>
         <v/>
       </c>
       <c r="M46" s="11" t="inlineStr">
@@ -4400,7 +4400,7 @@
         <v>387</v>
       </c>
       <c r="L47" s="10">
-        <f>ROUNDDOWN(K47*11.4,0)</f>
+        <f>ROUNDDOWN(K47*11.12,0)</f>
         <v/>
       </c>
       <c r="M47" s="11" t="inlineStr">
@@ -4471,7 +4471,7 @@
         <v>244</v>
       </c>
       <c r="L48" s="10">
-        <f>ROUNDDOWN(K48*11.4,0)</f>
+        <f>ROUNDDOWN(K48*11.12,0)</f>
         <v/>
       </c>
       <c r="M48" s="11" t="inlineStr">
@@ -4542,7 +4542,7 @@
         <v>244</v>
       </c>
       <c r="L49" s="10">
-        <f>ROUNDDOWN(K49*11.4,0)</f>
+        <f>ROUNDDOWN(K49*11.12,0)</f>
         <v/>
       </c>
       <c r="M49" s="11" t="inlineStr">
@@ -4613,7 +4613,7 @@
         <v>387</v>
       </c>
       <c r="L50" s="10">
-        <f>ROUNDDOWN(K50*11.4,0)</f>
+        <f>ROUNDDOWN(K50*11.12,0)</f>
         <v/>
       </c>
       <c r="M50" s="11" t="inlineStr">
@@ -4684,7 +4684,7 @@
         <v>179</v>
       </c>
       <c r="L51" s="10">
-        <f>ROUNDDOWN(K51*11.4,0)</f>
+        <f>ROUNDDOWN(K51*11.12,0)</f>
         <v/>
       </c>
       <c r="M51" s="11" t="inlineStr">
@@ -4755,7 +4755,7 @@
         <v>309</v>
       </c>
       <c r="L52" s="10">
-        <f>ROUNDDOWN(K52*11.4,0)</f>
+        <f>ROUNDDOWN(K52*11.12,0)</f>
         <v/>
       </c>
       <c r="M52" s="11" t="inlineStr">
@@ -4826,7 +4826,7 @@
         <v>220</v>
       </c>
       <c r="L53" s="10">
-        <f>ROUNDDOWN(K53*11.4,0)</f>
+        <f>ROUNDDOWN(K53*11.12,0)</f>
         <v/>
       </c>
       <c r="M53" s="11" t="inlineStr">
@@ -4897,7 +4897,7 @@
         <v>244</v>
       </c>
       <c r="L54" s="10">
-        <f>ROUNDDOWN(K54*11.4,0)</f>
+        <f>ROUNDDOWN(K54*11.12,0)</f>
         <v/>
       </c>
       <c r="M54" s="11" t="inlineStr">
@@ -4968,7 +4968,7 @@
         <v>244</v>
       </c>
       <c r="L55" s="10">
-        <f>ROUNDDOWN(K55*11.4,0)</f>
+        <f>ROUNDDOWN(K55*11.12,0)</f>
         <v/>
       </c>
       <c r="M55" s="11" t="inlineStr">
@@ -5039,7 +5039,7 @@
         <v>387</v>
       </c>
       <c r="L56" s="10">
-        <f>ROUNDDOWN(K56*11.4,0)</f>
+        <f>ROUNDDOWN(K56*11.12,0)</f>
         <v/>
       </c>
       <c r="M56" s="11" t="inlineStr">
@@ -5110,7 +5110,7 @@
         <v>309</v>
       </c>
       <c r="L57" s="10">
-        <f>ROUNDDOWN(K57*11.4,0)</f>
+        <f>ROUNDDOWN(K57*11.12,0)</f>
         <v/>
       </c>
       <c r="M57" s="11" t="inlineStr">
@@ -5181,7 +5181,7 @@
         <v>387</v>
       </c>
       <c r="L58" s="10">
-        <f>ROUNDDOWN(K58*11.4,0)</f>
+        <f>ROUNDDOWN(K58*11.12,0)</f>
         <v/>
       </c>
       <c r="M58" s="11" t="inlineStr">
@@ -5252,7 +5252,7 @@
         <v>244</v>
       </c>
       <c r="L59" s="10">
-        <f>ROUNDDOWN(K59*11.4,0)</f>
+        <f>ROUNDDOWN(K59*11.12,0)</f>
         <v/>
       </c>
       <c r="M59" s="11" t="inlineStr">
@@ -5323,7 +5323,7 @@
         <v>244</v>
       </c>
       <c r="L60" s="10">
-        <f>ROUNDDOWN(K60*11.4,0)</f>
+        <f>ROUNDDOWN(K60*11.12,0)</f>
         <v/>
       </c>
       <c r="M60" s="11" t="inlineStr">
@@ -5394,7 +5394,7 @@
         <v>387</v>
       </c>
       <c r="L61" s="10">
-        <f>ROUNDDOWN(K61*11.4,0)</f>
+        <f>ROUNDDOWN(K61*11.12,0)</f>
         <v/>
       </c>
       <c r="M61" s="11" t="inlineStr">
@@ -5465,7 +5465,7 @@
         <v>220</v>
       </c>
       <c r="L62" s="10">
-        <f>ROUNDDOWN(K62*11.4,0)</f>
+        <f>ROUNDDOWN(K62*11.12,0)</f>
         <v/>
       </c>
       <c r="M62" s="11" t="inlineStr">
@@ -5536,7 +5536,7 @@
         <v>387</v>
       </c>
       <c r="L63" s="10">
-        <f>ROUNDDOWN(K63*11.4,0)</f>
+        <f>ROUNDDOWN(K63*11.12,0)</f>
         <v/>
       </c>
       <c r="M63" s="11" t="inlineStr">
@@ -5607,7 +5607,7 @@
         <v>244</v>
       </c>
       <c r="L64" s="10">
-        <f>ROUNDDOWN(K64*11.4,0)</f>
+        <f>ROUNDDOWN(K64*11.12,0)</f>
         <v/>
       </c>
       <c r="M64" s="11" t="inlineStr">
@@ -5678,7 +5678,7 @@
         <v>244</v>
       </c>
       <c r="L65" s="10">
-        <f>ROUNDDOWN(K65*11.4,0)</f>
+        <f>ROUNDDOWN(K65*11.12,0)</f>
         <v/>
       </c>
       <c r="M65" s="11" t="inlineStr">
@@ -5749,7 +5749,7 @@
         <v>387</v>
       </c>
       <c r="L66" s="10">
-        <f>ROUNDDOWN(K66*11.4,0)</f>
+        <f>ROUNDDOWN(K66*11.12,0)</f>
         <v/>
       </c>
       <c r="M66" s="11" t="inlineStr">
@@ -5820,7 +5820,7 @@
         <v>179</v>
       </c>
       <c r="L67" s="10">
-        <f>ROUNDDOWN(K67*11.4,0)</f>
+        <f>ROUNDDOWN(K67*11.12,0)</f>
         <v/>
       </c>
       <c r="M67" s="11" t="inlineStr">
@@ -5891,7 +5891,7 @@
         <v>309</v>
       </c>
       <c r="L68" s="10">
-        <f>ROUNDDOWN(K68*11.4,0)</f>
+        <f>ROUNDDOWN(K68*11.12,0)</f>
         <v/>
       </c>
       <c r="M68" s="11" t="inlineStr">
@@ -5962,7 +5962,7 @@
         <v>220</v>
       </c>
       <c r="L69" s="10">
-        <f>ROUNDDOWN(K69*11.4,0)</f>
+        <f>ROUNDDOWN(K69*11.12,0)</f>
         <v/>
       </c>
       <c r="M69" s="11" t="inlineStr">
@@ -6033,7 +6033,7 @@
         <v>244</v>
       </c>
       <c r="L70" s="10">
-        <f>ROUNDDOWN(K70*11.4,0)</f>
+        <f>ROUNDDOWN(K70*11.12,0)</f>
         <v/>
       </c>
       <c r="M70" s="11" t="inlineStr">
@@ -6104,7 +6104,7 @@
         <v>244</v>
       </c>
       <c r="L71" s="10">
-        <f>ROUNDDOWN(K71*11.4,0)</f>
+        <f>ROUNDDOWN(K71*11.12,0)</f>
         <v/>
       </c>
       <c r="M71" s="11" t="inlineStr">
@@ -6175,7 +6175,7 @@
         <v>387</v>
       </c>
       <c r="L72" s="10">
-        <f>ROUNDDOWN(K72*11.4,0)</f>
+        <f>ROUNDDOWN(K72*11.12,0)</f>
         <v/>
       </c>
       <c r="M72" s="11" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>※金額は基本単位×11.40円（端数切捨て、1回ごと）。加算・利用者負担割合は未計上。</t>
+          <t>※記録一覧の金額は1回ごとの参考値。利用者別の合計はサービス提供票の別表と同じく合計単位×11.12円（端数切捨て）で計算すること。加算・利用者負担割合は未計上。</t>
         </is>
       </c>
     </row>
